--- a/SMART RSA-RCS Datasets.xlsx
+++ b/SMART RSA-RCS Datasets.xlsx
@@ -8,12 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\DCAL HYD 2026\Paper\Theme\Responsive Services or RCS\Conceptualization\FESA RSA RCS PACKAGE PROJECTS\SMART RSA RCS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83EFD447-6C12-45B6-82E2-A6C08403ABDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D798C66-3812-45B3-9B16-D4BC81028A74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Bulletin Board" sheetId="1" r:id="rId1"/>
+    <sheet name="B360 FESA Centre" sheetId="3" r:id="rId2"/>
+    <sheet name="Sheet1" sheetId="2" r:id="rId3"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -25,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="56">
   <si>
     <t>RSA No</t>
   </si>
@@ -163,6 +165,36 @@
   </si>
   <si>
     <t>BRSA_0005_Q0000</t>
+  </si>
+  <si>
+    <t>Not Active</t>
+  </si>
+  <si>
+    <t>In-time Adherence</t>
+  </si>
+  <si>
+    <t>Call to attention Aspects</t>
+  </si>
+  <si>
+    <t>Specific FESA Infrastructure and Resources</t>
+  </si>
+  <si>
+    <t>FESA Assist Actuation Centre Status</t>
+  </si>
+  <si>
+    <t>FESA RCS Guidelines  and Vehicles</t>
+  </si>
+  <si>
+    <t>FESA Theme Learning Centre Status</t>
+  </si>
+  <si>
+    <t>Type of FESA QOS - Reliable/ Linked/ SMART/ Befitting Emergency</t>
+  </si>
+  <si>
+    <t>FESA Risk / Hazard Category</t>
+  </si>
+  <si>
+    <t>FESA Notice Alert</t>
   </si>
 </sst>
 </file>
@@ -234,7 +266,7 @@
   </cellStyleXfs>
   <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -879,4 +911,376 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{31F51D46-88B1-476D-8CD7-42FBC0AD7317}">
+  <dimension ref="A1:S6"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="13.6640625" customWidth="1"/>
+    <col min="3" max="3" width="11.88671875" customWidth="1"/>
+    <col min="4" max="4" width="20" customWidth="1"/>
+    <col min="8" max="8" width="16" customWidth="1"/>
+    <col min="9" max="9" width="26.44140625" customWidth="1"/>
+    <col min="10" max="10" width="16" customWidth="1"/>
+    <col min="11" max="11" width="12.33203125" customWidth="1"/>
+    <col min="12" max="12" width="12.77734375" customWidth="1"/>
+    <col min="13" max="13" width="15.21875" customWidth="1"/>
+    <col min="14" max="15" width="14.77734375" customWidth="1"/>
+    <col min="17" max="17" width="14.6640625" customWidth="1"/>
+    <col min="18" max="18" width="23" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:19" ht="87" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="O1" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="P1" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q1" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="R1" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="2" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F2" s="3">
+        <v>46060</v>
+      </c>
+      <c r="G2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I2" t="s">
+        <v>25</v>
+      </c>
+      <c r="J2" t="s">
+        <v>27</v>
+      </c>
+      <c r="K2" t="s">
+        <v>26</v>
+      </c>
+      <c r="L2" t="s">
+        <v>22</v>
+      </c>
+      <c r="M2" t="s">
+        <v>26</v>
+      </c>
+      <c r="N2" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" t="s">
+        <v>24</v>
+      </c>
+      <c r="P2" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>29</v>
+      </c>
+      <c r="R2" t="s">
+        <v>30</v>
+      </c>
+      <c r="S2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D3" t="s">
+        <v>33</v>
+      </c>
+      <c r="E3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F3" s="3">
+        <v>46060</v>
+      </c>
+      <c r="G3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I3" t="s">
+        <v>34</v>
+      </c>
+      <c r="J3" t="s">
+        <v>27</v>
+      </c>
+      <c r="K3" t="s">
+        <v>46</v>
+      </c>
+      <c r="L3" t="s">
+        <v>22</v>
+      </c>
+      <c r="M3" t="s">
+        <v>46</v>
+      </c>
+      <c r="N3" t="s">
+        <v>46</v>
+      </c>
+      <c r="O3" t="s">
+        <v>24</v>
+      </c>
+      <c r="P3" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>29</v>
+      </c>
+      <c r="R3" t="s">
+        <v>30</v>
+      </c>
+      <c r="S3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>38</v>
+      </c>
+      <c r="C4" t="s">
+        <v>39</v>
+      </c>
+      <c r="D4" t="s">
+        <v>35</v>
+      </c>
+      <c r="E4" t="s">
+        <v>21</v>
+      </c>
+      <c r="F4" s="3">
+        <v>46060</v>
+      </c>
+      <c r="G4" t="s">
+        <v>22</v>
+      </c>
+      <c r="H4" t="s">
+        <v>23</v>
+      </c>
+      <c r="I4" t="s">
+        <v>36</v>
+      </c>
+      <c r="J4" t="s">
+        <v>27</v>
+      </c>
+      <c r="K4" t="s">
+        <v>46</v>
+      </c>
+      <c r="L4" t="s">
+        <v>22</v>
+      </c>
+      <c r="M4" t="s">
+        <v>26</v>
+      </c>
+      <c r="N4" t="s">
+        <v>46</v>
+      </c>
+      <c r="O4" t="s">
+        <v>24</v>
+      </c>
+      <c r="P4" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>29</v>
+      </c>
+      <c r="R4" t="s">
+        <v>30</v>
+      </c>
+      <c r="S4" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>37</v>
+      </c>
+      <c r="C5" t="s">
+        <v>40</v>
+      </c>
+      <c r="D5" t="s">
+        <v>41</v>
+      </c>
+      <c r="E5" t="s">
+        <v>21</v>
+      </c>
+      <c r="F5" s="3">
+        <v>46060</v>
+      </c>
+      <c r="G5" t="s">
+        <v>22</v>
+      </c>
+      <c r="H5" t="s">
+        <v>23</v>
+      </c>
+      <c r="I5" t="s">
+        <v>42</v>
+      </c>
+      <c r="J5" t="s">
+        <v>27</v>
+      </c>
+      <c r="K5" t="s">
+        <v>46</v>
+      </c>
+      <c r="L5" t="s">
+        <v>22</v>
+      </c>
+      <c r="M5" t="s">
+        <v>26</v>
+      </c>
+      <c r="N5" t="s">
+        <v>46</v>
+      </c>
+      <c r="O5" t="s">
+        <v>26</v>
+      </c>
+      <c r="P5" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>29</v>
+      </c>
+      <c r="R5" t="s">
+        <v>30</v>
+      </c>
+      <c r="S5" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>43</v>
+      </c>
+      <c r="C6" t="s">
+        <v>43</v>
+      </c>
+      <c r="D6" t="s">
+        <v>44</v>
+      </c>
+      <c r="E6" t="s">
+        <v>21</v>
+      </c>
+      <c r="F6" s="3">
+        <v>46060</v>
+      </c>
+      <c r="G6" t="s">
+        <v>22</v>
+      </c>
+      <c r="H6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I6" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="J6" t="s">
+        <v>27</v>
+      </c>
+      <c r="K6" t="s">
+        <v>46</v>
+      </c>
+      <c r="L6" t="s">
+        <v>22</v>
+      </c>
+      <c r="M6" t="s">
+        <v>46</v>
+      </c>
+      <c r="N6" t="s">
+        <v>46</v>
+      </c>
+      <c r="O6" t="s">
+        <v>24</v>
+      </c>
+      <c r="P6" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>29</v>
+      </c>
+      <c r="R6" t="s">
+        <v>30</v>
+      </c>
+      <c r="S6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5C081DE9-EF7F-4394-B2AD-7F39C156AD0A}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/SMART RSA-RCS Datasets.xlsx
+++ b/SMART RSA-RCS Datasets.xlsx
@@ -8,14 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\DCAL HYD 2026\Paper\Theme\Responsive Services or RCS\Conceptualization\FESA RSA RCS PACKAGE PROJECTS\SMART RSA RCS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D798C66-3812-45B3-9B16-D4BC81028A74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32CAD835-7964-4867-96C3-FAAD45B2C802}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Bulletin Board" sheetId="1" r:id="rId1"/>
-    <sheet name="B360 FESA Centre" sheetId="3" r:id="rId2"/>
-    <sheet name="Sheet1" sheetId="2" r:id="rId3"/>
+    <sheet name="B360 FESA Centre (2)" sheetId="4" r:id="rId2"/>
+    <sheet name="B360 Heart Centre" sheetId="3" r:id="rId3"/>
+    <sheet name="Sheet1" sheetId="2" r:id="rId4"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -27,17 +28,11 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="312" uniqueCount="67">
   <si>
     <t>RSA No</t>
   </si>
   <si>
-    <t>Ward or Taluk No</t>
-  </si>
-  <si>
-    <t>City/   Taluk</t>
-  </si>
-  <si>
     <t xml:space="preserve">RSA Status - Basic/                NEXT Step/              Advanced             </t>
   </si>
   <si>
@@ -74,9 +69,6 @@
     <t>RSA Package Subscription Type - GOVT/LINKED/ BOTH</t>
   </si>
   <si>
-    <t>RSA Package  Subscriber Name</t>
-  </si>
-  <si>
     <t>RSA Notice Alert</t>
   </si>
   <si>
@@ -195,6 +187,48 @@
   </si>
   <si>
     <t>FESA Notice Alert</t>
+  </si>
+  <si>
+    <t>City/   Taluk/ Zilla</t>
+  </si>
+  <si>
+    <t>Ward or Taluk or Zilla No</t>
+  </si>
+  <si>
+    <t>RSA Package Subscriber Name/Category</t>
+  </si>
+  <si>
+    <t>RSA Package  Subscriber Name/Category</t>
+  </si>
+  <si>
+    <t>Active - Linked</t>
+  </si>
+  <si>
+    <t>Specific Heart Cente Infrastructure and Resources</t>
+  </si>
+  <si>
+    <t>Heart Centre RCS Guidelines  and Vehicles</t>
+  </si>
+  <si>
+    <t>Heart Centre Assist Actuation Centre Status</t>
+  </si>
+  <si>
+    <t>Heart Centre Theme Learning Centre Status</t>
+  </si>
+  <si>
+    <t>Type of Heart Centre QOS - Reliable/ Linked/ SMART/ Befitting Emergency</t>
+  </si>
+  <si>
+    <t>Linked</t>
+  </si>
+  <si>
+    <t>Heart Centre Risk / Hazard Category</t>
+  </si>
+  <si>
+    <t>No dedicated Centre</t>
+  </si>
+  <si>
+    <t>Heart Centre Notice Alert</t>
   </si>
 </sst>
 </file>
@@ -571,341 +605,341 @@
   <sheetData>
     <row r="1" spans="1:19" ht="87" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>1</v>
+        <v>54</v>
       </c>
       <c r="C1" t="s">
         <v>0</v>
       </c>
       <c r="D1" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="M1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="E1" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="J1" s="2" t="s">
+      <c r="N1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="K1" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="L1" s="2" t="s">
+      <c r="O1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="M1" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="N1" s="2" t="s">
+      <c r="P1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="O1" s="2" t="s">
+      <c r="Q1" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="R1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="P1" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="Q1" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="R1" s="2" t="s">
+      <c r="S1" s="1" t="s">
         <v>13</v>
-      </c>
-      <c r="S1" s="1" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="2" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C2" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="D2" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E2" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F2" s="3">
         <v>46060</v>
       </c>
       <c r="G2" t="s">
+        <v>19</v>
+      </c>
+      <c r="H2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I2" t="s">
         <v>22</v>
       </c>
-      <c r="H2" t="s">
+      <c r="J2" t="s">
+        <v>24</v>
+      </c>
+      <c r="K2" t="s">
+        <v>21</v>
+      </c>
+      <c r="L2" t="s">
+        <v>21</v>
+      </c>
+      <c r="M2" t="s">
         <v>23</v>
       </c>
-      <c r="I2" t="s">
-        <v>25</v>
-      </c>
-      <c r="J2" t="s">
+      <c r="N2" t="s">
+        <v>24</v>
+      </c>
+      <c r="O2" t="s">
+        <v>21</v>
+      </c>
+      <c r="P2" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>26</v>
+      </c>
+      <c r="R2" t="s">
         <v>27</v>
       </c>
-      <c r="K2" t="s">
-        <v>24</v>
-      </c>
-      <c r="L2" t="s">
-        <v>24</v>
-      </c>
-      <c r="M2" t="s">
-        <v>26</v>
-      </c>
-      <c r="N2" t="s">
-        <v>27</v>
-      </c>
-      <c r="O2" t="s">
-        <v>24</v>
-      </c>
-      <c r="P2" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q2" t="s">
-        <v>29</v>
-      </c>
-      <c r="R2" t="s">
-        <v>30</v>
-      </c>
       <c r="S2" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="C3" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="D3" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="E3" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F3" s="3">
         <v>46060</v>
       </c>
       <c r="G3" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="H3" t="s">
+        <v>20</v>
+      </c>
+      <c r="I3" t="s">
+        <v>31</v>
+      </c>
+      <c r="J3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L3" t="s">
         <v>23</v>
       </c>
-      <c r="I3" t="s">
-        <v>34</v>
-      </c>
-      <c r="J3" t="s">
+      <c r="M3" t="s">
+        <v>23</v>
+      </c>
+      <c r="N3" t="s">
+        <v>24</v>
+      </c>
+      <c r="O3" t="s">
+        <v>21</v>
+      </c>
+      <c r="P3" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>26</v>
+      </c>
+      <c r="R3" t="s">
         <v>27</v>
       </c>
-      <c r="K3" t="s">
-        <v>24</v>
-      </c>
-      <c r="L3" t="s">
-        <v>26</v>
-      </c>
-      <c r="M3" t="s">
-        <v>26</v>
-      </c>
-      <c r="N3" t="s">
-        <v>27</v>
-      </c>
-      <c r="O3" t="s">
-        <v>24</v>
-      </c>
-      <c r="P3" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q3" t="s">
-        <v>29</v>
-      </c>
-      <c r="R3" t="s">
-        <v>30</v>
-      </c>
       <c r="S3" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C4" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="D4" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="E4" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F4" s="3">
         <v>46060</v>
       </c>
       <c r="G4" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="H4" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="I4" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="J4" t="s">
+        <v>24</v>
+      </c>
+      <c r="K4" t="s">
+        <v>21</v>
+      </c>
+      <c r="L4" t="s">
+        <v>21</v>
+      </c>
+      <c r="M4" t="s">
+        <v>21</v>
+      </c>
+      <c r="N4" t="s">
+        <v>24</v>
+      </c>
+      <c r="O4" t="s">
+        <v>21</v>
+      </c>
+      <c r="P4" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>26</v>
+      </c>
+      <c r="R4" t="s">
         <v>27</v>
       </c>
-      <c r="K4" t="s">
-        <v>24</v>
-      </c>
-      <c r="L4" t="s">
-        <v>24</v>
-      </c>
-      <c r="M4" t="s">
-        <v>24</v>
-      </c>
-      <c r="N4" t="s">
-        <v>27</v>
-      </c>
-      <c r="O4" t="s">
-        <v>24</v>
-      </c>
-      <c r="P4" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q4" t="s">
-        <v>29</v>
-      </c>
-      <c r="R4" t="s">
-        <v>30</v>
-      </c>
       <c r="S4" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
+        <v>34</v>
+      </c>
+      <c r="C5" t="s">
         <v>37</v>
       </c>
-      <c r="C5" t="s">
-        <v>40</v>
-      </c>
       <c r="D5" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="E5" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F5" s="3">
         <v>46060</v>
       </c>
       <c r="G5" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="H5" t="s">
+        <v>20</v>
+      </c>
+      <c r="I5" t="s">
+        <v>39</v>
+      </c>
+      <c r="J5" t="s">
+        <v>24</v>
+      </c>
+      <c r="K5" t="s">
+        <v>21</v>
+      </c>
+      <c r="L5" t="s">
+        <v>21</v>
+      </c>
+      <c r="M5" t="s">
+        <v>21</v>
+      </c>
+      <c r="N5" t="s">
+        <v>24</v>
+      </c>
+      <c r="O5" t="s">
         <v>23</v>
       </c>
-      <c r="I5" t="s">
-        <v>42</v>
-      </c>
-      <c r="J5" t="s">
+      <c r="P5" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>26</v>
+      </c>
+      <c r="R5" t="s">
         <v>27</v>
       </c>
-      <c r="K5" t="s">
-        <v>24</v>
-      </c>
-      <c r="L5" t="s">
-        <v>24</v>
-      </c>
-      <c r="M5" t="s">
-        <v>24</v>
-      </c>
-      <c r="N5" t="s">
-        <v>27</v>
-      </c>
-      <c r="O5" t="s">
-        <v>26</v>
-      </c>
-      <c r="P5" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q5" t="s">
-        <v>29</v>
-      </c>
-      <c r="R5" t="s">
-        <v>30</v>
-      </c>
       <c r="S5" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="C6" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="D6" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="E6" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F6" s="3">
         <v>46060</v>
       </c>
       <c r="G6" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="H6" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="I6" s="4" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="J6" t="s">
+        <v>24</v>
+      </c>
+      <c r="K6" t="s">
+        <v>21</v>
+      </c>
+      <c r="L6" t="s">
+        <v>21</v>
+      </c>
+      <c r="M6" t="s">
+        <v>21</v>
+      </c>
+      <c r="N6" t="s">
+        <v>24</v>
+      </c>
+      <c r="O6" t="s">
+        <v>21</v>
+      </c>
+      <c r="P6" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>26</v>
+      </c>
+      <c r="R6" t="s">
         <v>27</v>
       </c>
-      <c r="K6" t="s">
-        <v>24</v>
-      </c>
-      <c r="L6" t="s">
-        <v>24</v>
-      </c>
-      <c r="M6" t="s">
-        <v>24</v>
-      </c>
-      <c r="N6" t="s">
-        <v>27</v>
-      </c>
-      <c r="O6" t="s">
-        <v>24</v>
-      </c>
-      <c r="P6" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q6" t="s">
-        <v>29</v>
-      </c>
-      <c r="R6" t="s">
-        <v>30</v>
-      </c>
       <c r="S6" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
     </row>
   </sheetData>
@@ -914,6 +948,369 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A4790F37-4283-4D7E-AF8C-DD0A34BBAF84}">
+  <dimension ref="A1:S6"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="13.6640625" customWidth="1"/>
+    <col min="3" max="3" width="11.88671875" customWidth="1"/>
+    <col min="4" max="4" width="20" customWidth="1"/>
+    <col min="8" max="8" width="16" customWidth="1"/>
+    <col min="9" max="9" width="26.44140625" customWidth="1"/>
+    <col min="10" max="10" width="16" customWidth="1"/>
+    <col min="11" max="11" width="12.33203125" customWidth="1"/>
+    <col min="12" max="12" width="12.77734375" customWidth="1"/>
+    <col min="13" max="13" width="15.21875" customWidth="1"/>
+    <col min="14" max="15" width="14.77734375" customWidth="1"/>
+    <col min="17" max="17" width="14.6640625" customWidth="1"/>
+    <col min="18" max="18" width="23" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:19" ht="87" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="O1" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="P1" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="Q1" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="R1" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="2" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F2" s="3">
+        <v>46060</v>
+      </c>
+      <c r="G2" t="s">
+        <v>19</v>
+      </c>
+      <c r="H2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J2" t="s">
+        <v>24</v>
+      </c>
+      <c r="K2" t="s">
+        <v>23</v>
+      </c>
+      <c r="L2" t="s">
+        <v>19</v>
+      </c>
+      <c r="M2" t="s">
+        <v>23</v>
+      </c>
+      <c r="N2" t="s">
+        <v>43</v>
+      </c>
+      <c r="O2" t="s">
+        <v>21</v>
+      </c>
+      <c r="P2" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>26</v>
+      </c>
+      <c r="R2" t="s">
+        <v>27</v>
+      </c>
+      <c r="S2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D3" t="s">
+        <v>30</v>
+      </c>
+      <c r="E3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F3" s="3">
+        <v>46060</v>
+      </c>
+      <c r="G3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H3" t="s">
+        <v>20</v>
+      </c>
+      <c r="I3" t="s">
+        <v>31</v>
+      </c>
+      <c r="J3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K3" t="s">
+        <v>43</v>
+      </c>
+      <c r="L3" t="s">
+        <v>19</v>
+      </c>
+      <c r="M3" t="s">
+        <v>43</v>
+      </c>
+      <c r="N3" t="s">
+        <v>43</v>
+      </c>
+      <c r="O3" t="s">
+        <v>21</v>
+      </c>
+      <c r="P3" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>26</v>
+      </c>
+      <c r="R3" t="s">
+        <v>27</v>
+      </c>
+      <c r="S3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>35</v>
+      </c>
+      <c r="C4" t="s">
+        <v>36</v>
+      </c>
+      <c r="D4" t="s">
+        <v>32</v>
+      </c>
+      <c r="E4" t="s">
+        <v>18</v>
+      </c>
+      <c r="F4" s="3">
+        <v>46060</v>
+      </c>
+      <c r="G4" t="s">
+        <v>19</v>
+      </c>
+      <c r="H4" t="s">
+        <v>20</v>
+      </c>
+      <c r="I4" t="s">
+        <v>33</v>
+      </c>
+      <c r="J4" t="s">
+        <v>24</v>
+      </c>
+      <c r="K4" t="s">
+        <v>43</v>
+      </c>
+      <c r="L4" t="s">
+        <v>19</v>
+      </c>
+      <c r="M4" t="s">
+        <v>23</v>
+      </c>
+      <c r="N4" t="s">
+        <v>43</v>
+      </c>
+      <c r="O4" t="s">
+        <v>21</v>
+      </c>
+      <c r="P4" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>26</v>
+      </c>
+      <c r="R4" t="s">
+        <v>27</v>
+      </c>
+      <c r="S4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>34</v>
+      </c>
+      <c r="C5" t="s">
+        <v>37</v>
+      </c>
+      <c r="D5" t="s">
+        <v>38</v>
+      </c>
+      <c r="E5" t="s">
+        <v>18</v>
+      </c>
+      <c r="F5" s="3">
+        <v>46060</v>
+      </c>
+      <c r="G5" t="s">
+        <v>19</v>
+      </c>
+      <c r="H5" t="s">
+        <v>20</v>
+      </c>
+      <c r="I5" t="s">
+        <v>39</v>
+      </c>
+      <c r="J5" t="s">
+        <v>24</v>
+      </c>
+      <c r="K5" t="s">
+        <v>43</v>
+      </c>
+      <c r="L5" t="s">
+        <v>19</v>
+      </c>
+      <c r="M5" t="s">
+        <v>23</v>
+      </c>
+      <c r="N5" t="s">
+        <v>43</v>
+      </c>
+      <c r="O5" t="s">
+        <v>23</v>
+      </c>
+      <c r="P5" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>26</v>
+      </c>
+      <c r="R5" t="s">
+        <v>27</v>
+      </c>
+      <c r="S5" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>40</v>
+      </c>
+      <c r="C6" t="s">
+        <v>40</v>
+      </c>
+      <c r="D6" t="s">
+        <v>41</v>
+      </c>
+      <c r="E6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F6" s="3">
+        <v>46060</v>
+      </c>
+      <c r="G6" t="s">
+        <v>19</v>
+      </c>
+      <c r="H6" t="s">
+        <v>20</v>
+      </c>
+      <c r="I6" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="J6" t="s">
+        <v>24</v>
+      </c>
+      <c r="K6" t="s">
+        <v>43</v>
+      </c>
+      <c r="L6" t="s">
+        <v>19</v>
+      </c>
+      <c r="M6" t="s">
+        <v>43</v>
+      </c>
+      <c r="N6" t="s">
+        <v>43</v>
+      </c>
+      <c r="O6" t="s">
+        <v>21</v>
+      </c>
+      <c r="P6" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>26</v>
+      </c>
+      <c r="R6" t="s">
+        <v>27</v>
+      </c>
+      <c r="S6" t="s">
+        <v>21</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{31F51D46-88B1-476D-8CD7-42FBC0AD7317}">
   <dimension ref="A1:S6"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -934,341 +1331,341 @@
   <sheetData>
     <row r="1" spans="1:19" ht="87" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>1</v>
+        <v>54</v>
       </c>
       <c r="C1" t="s">
         <v>0</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>15</v>
+        <v>56</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>2</v>
+        <v>53</v>
       </c>
       <c r="F1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="J1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="J1" s="2" t="s">
-        <v>8</v>
-      </c>
       <c r="K1" s="2" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="L1" s="2" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="N1" s="2" t="s">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="O1" s="2" t="s">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="P1" s="2" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="Q1" s="2" t="s">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="R1" s="2" t="s">
-        <v>54</v>
+        <v>64</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
     </row>
     <row r="2" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C2" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="D2" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E2" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F2" s="3">
         <v>46060</v>
       </c>
       <c r="G2" t="s">
+        <v>19</v>
+      </c>
+      <c r="H2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I2" t="s">
         <v>22</v>
       </c>
-      <c r="H2" t="s">
+      <c r="J2" t="s">
+        <v>57</v>
+      </c>
+      <c r="K2" t="s">
         <v>23</v>
       </c>
-      <c r="I2" t="s">
-        <v>25</v>
-      </c>
-      <c r="J2" t="s">
-        <v>27</v>
-      </c>
-      <c r="K2" t="s">
-        <v>26</v>
-      </c>
       <c r="L2" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="M2" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="N2" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="O2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="P2" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="Q2" t="s">
-        <v>29</v>
+        <v>63</v>
       </c>
       <c r="R2" t="s">
-        <v>30</v>
+        <v>65</v>
       </c>
       <c r="S2" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="C3" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="D3" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="E3" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F3" s="3">
         <v>46060</v>
       </c>
       <c r="G3" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="H3" t="s">
+        <v>20</v>
+      </c>
+      <c r="I3" t="s">
+        <v>31</v>
+      </c>
+      <c r="J3" t="s">
+        <v>57</v>
+      </c>
+      <c r="K3" t="s">
         <v>23</v>
       </c>
-      <c r="I3" t="s">
-        <v>34</v>
-      </c>
-      <c r="J3" t="s">
-        <v>27</v>
-      </c>
-      <c r="K3" t="s">
-        <v>46</v>
-      </c>
       <c r="L3" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="M3" t="s">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="N3" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="O3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="P3" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="Q3" t="s">
-        <v>29</v>
+        <v>63</v>
       </c>
       <c r="R3" t="s">
-        <v>30</v>
+        <v>65</v>
       </c>
       <c r="S3" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C4" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="D4" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="E4" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F4" s="3">
         <v>46060</v>
       </c>
       <c r="G4" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="H4" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="I4" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="J4" t="s">
-        <v>27</v>
+        <v>43</v>
       </c>
       <c r="K4" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="L4" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="M4" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="N4" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="O4" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="P4" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="Q4" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="R4" t="s">
-        <v>30</v>
+        <v>65</v>
       </c>
       <c r="S4" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
+        <v>34</v>
+      </c>
+      <c r="C5" t="s">
         <v>37</v>
       </c>
-      <c r="C5" t="s">
-        <v>40</v>
-      </c>
       <c r="D5" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="E5" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F5" s="3">
         <v>46060</v>
       </c>
       <c r="G5" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="H5" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="I5" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="J5" t="s">
-        <v>27</v>
+        <v>43</v>
       </c>
       <c r="K5" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="L5" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="M5" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="N5" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="O5" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="P5" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="Q5" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="R5" t="s">
-        <v>30</v>
+        <v>65</v>
       </c>
       <c r="S5" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="C6" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="D6" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="E6" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F6" s="3">
         <v>46060</v>
       </c>
       <c r="G6" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="H6" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="I6" s="4" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="J6" t="s">
-        <v>27</v>
+        <v>43</v>
       </c>
       <c r="K6" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="L6" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="M6" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="N6" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="O6" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="P6" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="Q6" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="R6" t="s">
-        <v>30</v>
+        <v>65</v>
       </c>
       <c r="S6" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
     </row>
   </sheetData>
@@ -1276,7 +1673,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5C081DE9-EF7F-4394-B2AD-7F39C156AD0A}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>

--- a/SMART RSA-RCS Datasets.xlsx
+++ b/SMART RSA-RCS Datasets.xlsx
@@ -8,15 +8,18 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\DCAL HYD 2026\Paper\Theme\Responsive Services or RCS\Conceptualization\FESA RSA RCS PACKAGE PROJECTS\SMART RSA RCS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32CAD835-7964-4867-96C3-FAAD45B2C802}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CF7DC71-9666-428A-85ED-463D0E4B20A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Bulletin Board" sheetId="1" r:id="rId1"/>
-    <sheet name="B360 FESA Centre (2)" sheetId="4" r:id="rId2"/>
-    <sheet name="B360 Heart Centre" sheetId="3" r:id="rId3"/>
-    <sheet name="Sheet1" sheetId="2" r:id="rId4"/>
+    <sheet name="B360 FESA Centre" sheetId="4" r:id="rId2"/>
+    <sheet name="B360 Heart Centre" sheetId="5" r:id="rId3"/>
+    <sheet name="B360 MCB Centre" sheetId="6" r:id="rId4"/>
+    <sheet name="B360 DS Centre" sheetId="7" r:id="rId5"/>
+    <sheet name="B360 Suraksha Centre" sheetId="3" r:id="rId6"/>
+    <sheet name="Sheet1" sheetId="2" r:id="rId7"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -28,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="312" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="624" uniqueCount="95">
   <si>
     <t>RSA No</t>
   </si>
@@ -204,9 +207,6 @@
     <t>Active - Linked</t>
   </si>
   <si>
-    <t>Specific Heart Cente Infrastructure and Resources</t>
-  </si>
-  <si>
     <t>Heart Centre RCS Guidelines  and Vehicles</t>
   </si>
   <si>
@@ -229,6 +229,93 @@
   </si>
   <si>
     <t>Heart Centre Notice Alert</t>
+  </si>
+  <si>
+    <t>Maternit Care and Birthing Centre Status</t>
+  </si>
+  <si>
+    <t>MCB Centre RCS Guidelines  and Vehicles</t>
+  </si>
+  <si>
+    <t>MCB Centre Assist Actuation Centre Status</t>
+  </si>
+  <si>
+    <t>MCB Centre Theme Learning Centre Status</t>
+  </si>
+  <si>
+    <t>Type of MCB Centre QOS - Reliable/ Linked/ SMART/ Befitting Emergency</t>
+  </si>
+  <si>
+    <t>MCB Centre Risk / Hazard Category</t>
+  </si>
+  <si>
+    <t>MCB Centre Notice Alert</t>
+  </si>
+  <si>
+    <t>Advanced</t>
+  </si>
+  <si>
+    <t>SMART</t>
+  </si>
+  <si>
+    <t>Befitting Emergency</t>
+  </si>
+  <si>
+    <t>Dedicated Centre</t>
+  </si>
+  <si>
+    <t>LINKED</t>
+  </si>
+  <si>
+    <t>Acrive</t>
+  </si>
+  <si>
+    <t>DS Centre RCS Guidelines  and Vehicles</t>
+  </si>
+  <si>
+    <t>DS Centre Assist Actuation Centre Status</t>
+  </si>
+  <si>
+    <t>DS Centre Theme Learning Centre Status</t>
+  </si>
+  <si>
+    <t>Type of DS Centre QOS - Reliable/ Linked/ SMART/ Befitting Emergency</t>
+  </si>
+  <si>
+    <t>Specific RSA Suraksha Centre Infrastructure and Resources</t>
+  </si>
+  <si>
+    <t>Specific Heart Centre Infrastructure and Resources</t>
+  </si>
+  <si>
+    <t>Specific MCB Centre Infrastructure and Resources</t>
+  </si>
+  <si>
+    <t>Specific DS Centre Infrastructure and Resources</t>
+  </si>
+  <si>
+    <t>RSA Suraksha Centre RCS Guidelines  and Vehicles</t>
+  </si>
+  <si>
+    <t>RSA Suraksha Centre Assist Actuation Centre Status</t>
+  </si>
+  <si>
+    <t>RSA Suraksha Centre Theme Learning Centre Status</t>
+  </si>
+  <si>
+    <t>Type of RSA Suraksha Centre QOS - Reliable/ Linked/ SMART/ Befitting Emergency</t>
+  </si>
+  <si>
+    <t>DS Centre Risk / Hazard Category</t>
+  </si>
+  <si>
+    <t>DS Centre Notice Alert</t>
+  </si>
+  <si>
+    <t>RSA Suraksha Centre Risk / Hazard Category</t>
+  </si>
+  <si>
+    <t>RSA Suraksha Centre Notice Alert</t>
   </si>
 </sst>
 </file>
@@ -1311,7 +1398,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{31F51D46-88B1-476D-8CD7-42FBC0AD7317}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{78461931-1398-48AA-A3C5-E457044B9784}">
   <dimension ref="A1:S6"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -1367,25 +1454,25 @@
         <v>44</v>
       </c>
       <c r="M1" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="N1" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="O1" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="O1" s="2" t="s">
+      <c r="P1" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="P1" s="2" t="s">
+      <c r="Q1" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="Q1" s="2" t="s">
-        <v>62</v>
-      </c>
       <c r="R1" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="2" spans="1:19" x14ac:dyDescent="0.3">
@@ -1408,7 +1495,7 @@
         <v>19</v>
       </c>
       <c r="H2" t="s">
-        <v>20</v>
+        <v>77</v>
       </c>
       <c r="I2" t="s">
         <v>22</v>
@@ -1435,10 +1522,10 @@
         <v>21</v>
       </c>
       <c r="Q2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="R2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="S2" t="s">
         <v>21</v>
@@ -1464,7 +1551,7 @@
         <v>19</v>
       </c>
       <c r="H3" t="s">
-        <v>20</v>
+        <v>77</v>
       </c>
       <c r="I3" t="s">
         <v>31</v>
@@ -1491,10 +1578,10 @@
         <v>21</v>
       </c>
       <c r="Q3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="R3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="S3" t="s">
         <v>21</v>
@@ -1550,7 +1637,7 @@
         <v>21</v>
       </c>
       <c r="R4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="S4" t="s">
         <v>21</v>
@@ -1606,7 +1693,7 @@
         <v>21</v>
       </c>
       <c r="R5" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="S5" t="s">
         <v>21</v>
@@ -1662,7 +1749,7 @@
         <v>21</v>
       </c>
       <c r="R6" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="S6" t="s">
         <v>21</v>
@@ -1674,6 +1761,1095 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{113FC901-1BFF-4CEB-99B5-C6AA501E6BB7}">
+  <dimension ref="A1:S6"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="13.6640625" customWidth="1"/>
+    <col min="3" max="3" width="11.88671875" customWidth="1"/>
+    <col min="4" max="4" width="20" customWidth="1"/>
+    <col min="8" max="8" width="16" customWidth="1"/>
+    <col min="9" max="9" width="26.44140625" customWidth="1"/>
+    <col min="10" max="10" width="16" customWidth="1"/>
+    <col min="11" max="11" width="12.33203125" customWidth="1"/>
+    <col min="12" max="12" width="12.77734375" customWidth="1"/>
+    <col min="13" max="13" width="15.21875" customWidth="1"/>
+    <col min="14" max="15" width="14.77734375" customWidth="1"/>
+    <col min="17" max="17" width="19.21875" customWidth="1"/>
+    <col min="18" max="18" width="23" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:19" ht="87" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="O1" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="P1" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="Q1" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="R1" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="2" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F2" s="3">
+        <v>46060</v>
+      </c>
+      <c r="G2" t="s">
+        <v>19</v>
+      </c>
+      <c r="H2" t="s">
+        <v>77</v>
+      </c>
+      <c r="I2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J2" t="s">
+        <v>57</v>
+      </c>
+      <c r="K2" t="s">
+        <v>23</v>
+      </c>
+      <c r="L2" t="s">
+        <v>19</v>
+      </c>
+      <c r="M2" t="s">
+        <v>23</v>
+      </c>
+      <c r="N2" t="s">
+        <v>43</v>
+      </c>
+      <c r="O2" t="s">
+        <v>23</v>
+      </c>
+      <c r="P2" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>62</v>
+      </c>
+      <c r="R2" t="s">
+        <v>64</v>
+      </c>
+      <c r="S2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D3" t="s">
+        <v>30</v>
+      </c>
+      <c r="E3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F3" s="3">
+        <v>46060</v>
+      </c>
+      <c r="G3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H3" t="s">
+        <v>77</v>
+      </c>
+      <c r="I3" t="s">
+        <v>31</v>
+      </c>
+      <c r="J3" t="s">
+        <v>23</v>
+      </c>
+      <c r="K3" t="s">
+        <v>23</v>
+      </c>
+      <c r="L3" t="s">
+        <v>73</v>
+      </c>
+      <c r="M3" t="s">
+        <v>73</v>
+      </c>
+      <c r="N3" t="s">
+        <v>74</v>
+      </c>
+      <c r="O3" t="s">
+        <v>73</v>
+      </c>
+      <c r="P3" t="s">
+        <v>74</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>75</v>
+      </c>
+      <c r="R3" t="s">
+        <v>76</v>
+      </c>
+      <c r="S3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>35</v>
+      </c>
+      <c r="C4" t="s">
+        <v>36</v>
+      </c>
+      <c r="D4" t="s">
+        <v>32</v>
+      </c>
+      <c r="E4" t="s">
+        <v>18</v>
+      </c>
+      <c r="F4" s="3">
+        <v>46060</v>
+      </c>
+      <c r="G4" t="s">
+        <v>19</v>
+      </c>
+      <c r="H4" t="s">
+        <v>20</v>
+      </c>
+      <c r="I4" t="s">
+        <v>33</v>
+      </c>
+      <c r="J4" t="s">
+        <v>43</v>
+      </c>
+      <c r="K4" t="s">
+        <v>43</v>
+      </c>
+      <c r="L4" t="s">
+        <v>19</v>
+      </c>
+      <c r="M4" t="s">
+        <v>43</v>
+      </c>
+      <c r="N4" t="s">
+        <v>43</v>
+      </c>
+      <c r="O4" t="s">
+        <v>21</v>
+      </c>
+      <c r="P4" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>21</v>
+      </c>
+      <c r="R4" t="s">
+        <v>64</v>
+      </c>
+      <c r="S4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>34</v>
+      </c>
+      <c r="C5" t="s">
+        <v>37</v>
+      </c>
+      <c r="D5" t="s">
+        <v>38</v>
+      </c>
+      <c r="E5" t="s">
+        <v>18</v>
+      </c>
+      <c r="F5" s="3">
+        <v>46060</v>
+      </c>
+      <c r="G5" t="s">
+        <v>19</v>
+      </c>
+      <c r="H5" t="s">
+        <v>20</v>
+      </c>
+      <c r="I5" t="s">
+        <v>39</v>
+      </c>
+      <c r="J5" t="s">
+        <v>43</v>
+      </c>
+      <c r="K5" t="s">
+        <v>43</v>
+      </c>
+      <c r="L5" t="s">
+        <v>19</v>
+      </c>
+      <c r="M5" t="s">
+        <v>43</v>
+      </c>
+      <c r="N5" t="s">
+        <v>43</v>
+      </c>
+      <c r="O5" t="s">
+        <v>21</v>
+      </c>
+      <c r="P5" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>21</v>
+      </c>
+      <c r="R5" t="s">
+        <v>64</v>
+      </c>
+      <c r="S5" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>40</v>
+      </c>
+      <c r="C6" t="s">
+        <v>40</v>
+      </c>
+      <c r="D6" t="s">
+        <v>41</v>
+      </c>
+      <c r="E6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F6" s="3">
+        <v>46060</v>
+      </c>
+      <c r="G6" t="s">
+        <v>19</v>
+      </c>
+      <c r="H6" t="s">
+        <v>20</v>
+      </c>
+      <c r="I6" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="J6" t="s">
+        <v>43</v>
+      </c>
+      <c r="K6" t="s">
+        <v>43</v>
+      </c>
+      <c r="L6" t="s">
+        <v>19</v>
+      </c>
+      <c r="M6" t="s">
+        <v>43</v>
+      </c>
+      <c r="N6" t="s">
+        <v>43</v>
+      </c>
+      <c r="O6" t="s">
+        <v>21</v>
+      </c>
+      <c r="P6" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>21</v>
+      </c>
+      <c r="R6" t="s">
+        <v>64</v>
+      </c>
+      <c r="S6" t="s">
+        <v>21</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4736391B-D21A-4B47-98EC-5AB45B4B5F5F}">
+  <dimension ref="A1:S6"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="13.6640625" customWidth="1"/>
+    <col min="3" max="3" width="11.88671875" customWidth="1"/>
+    <col min="4" max="4" width="20" customWidth="1"/>
+    <col min="8" max="8" width="16" customWidth="1"/>
+    <col min="9" max="9" width="26.44140625" customWidth="1"/>
+    <col min="10" max="10" width="16" customWidth="1"/>
+    <col min="11" max="11" width="12.33203125" customWidth="1"/>
+    <col min="12" max="12" width="12.77734375" customWidth="1"/>
+    <col min="13" max="13" width="15.21875" customWidth="1"/>
+    <col min="14" max="15" width="14.77734375" customWidth="1"/>
+    <col min="17" max="17" width="19.21875" customWidth="1"/>
+    <col min="18" max="18" width="23" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:19" ht="87" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="O1" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="P1" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="Q1" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="R1" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="2" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F2" s="3">
+        <v>46060</v>
+      </c>
+      <c r="G2" t="s">
+        <v>19</v>
+      </c>
+      <c r="H2" t="s">
+        <v>77</v>
+      </c>
+      <c r="I2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J2" t="s">
+        <v>23</v>
+      </c>
+      <c r="K2" t="s">
+        <v>23</v>
+      </c>
+      <c r="L2" t="s">
+        <v>73</v>
+      </c>
+      <c r="M2" t="s">
+        <v>73</v>
+      </c>
+      <c r="N2" t="s">
+        <v>74</v>
+      </c>
+      <c r="O2" t="s">
+        <v>73</v>
+      </c>
+      <c r="P2" t="s">
+        <v>74</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>75</v>
+      </c>
+      <c r="R2" t="s">
+        <v>76</v>
+      </c>
+      <c r="S2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D3" t="s">
+        <v>30</v>
+      </c>
+      <c r="E3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F3" s="3">
+        <v>46060</v>
+      </c>
+      <c r="G3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H3" t="s">
+        <v>77</v>
+      </c>
+      <c r="I3" t="s">
+        <v>31</v>
+      </c>
+      <c r="J3" t="s">
+        <v>57</v>
+      </c>
+      <c r="K3" t="s">
+        <v>23</v>
+      </c>
+      <c r="L3" t="s">
+        <v>26</v>
+      </c>
+      <c r="M3" t="s">
+        <v>78</v>
+      </c>
+      <c r="N3" t="s">
+        <v>23</v>
+      </c>
+      <c r="O3" t="s">
+        <v>23</v>
+      </c>
+      <c r="P3" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>74</v>
+      </c>
+      <c r="R3" t="s">
+        <v>64</v>
+      </c>
+      <c r="S3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>35</v>
+      </c>
+      <c r="C4" t="s">
+        <v>36</v>
+      </c>
+      <c r="D4" t="s">
+        <v>32</v>
+      </c>
+      <c r="E4" t="s">
+        <v>18</v>
+      </c>
+      <c r="F4" s="3">
+        <v>46060</v>
+      </c>
+      <c r="G4" t="s">
+        <v>19</v>
+      </c>
+      <c r="H4" t="s">
+        <v>20</v>
+      </c>
+      <c r="I4" t="s">
+        <v>33</v>
+      </c>
+      <c r="J4" t="s">
+        <v>43</v>
+      </c>
+      <c r="K4" t="s">
+        <v>43</v>
+      </c>
+      <c r="L4" t="s">
+        <v>19</v>
+      </c>
+      <c r="M4" t="s">
+        <v>43</v>
+      </c>
+      <c r="N4" t="s">
+        <v>43</v>
+      </c>
+      <c r="O4" t="s">
+        <v>21</v>
+      </c>
+      <c r="P4" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>21</v>
+      </c>
+      <c r="R4" t="s">
+        <v>64</v>
+      </c>
+      <c r="S4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>34</v>
+      </c>
+      <c r="C5" t="s">
+        <v>37</v>
+      </c>
+      <c r="D5" t="s">
+        <v>38</v>
+      </c>
+      <c r="E5" t="s">
+        <v>18</v>
+      </c>
+      <c r="F5" s="3">
+        <v>46060</v>
+      </c>
+      <c r="G5" t="s">
+        <v>19</v>
+      </c>
+      <c r="H5" t="s">
+        <v>20</v>
+      </c>
+      <c r="I5" t="s">
+        <v>39</v>
+      </c>
+      <c r="J5" t="s">
+        <v>43</v>
+      </c>
+      <c r="K5" t="s">
+        <v>43</v>
+      </c>
+      <c r="L5" t="s">
+        <v>19</v>
+      </c>
+      <c r="M5" t="s">
+        <v>43</v>
+      </c>
+      <c r="N5" t="s">
+        <v>43</v>
+      </c>
+      <c r="O5" t="s">
+        <v>21</v>
+      </c>
+      <c r="P5" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>21</v>
+      </c>
+      <c r="R5" t="s">
+        <v>64</v>
+      </c>
+      <c r="S5" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>40</v>
+      </c>
+      <c r="C6" t="s">
+        <v>40</v>
+      </c>
+      <c r="D6" t="s">
+        <v>41</v>
+      </c>
+      <c r="E6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F6" s="3">
+        <v>46060</v>
+      </c>
+      <c r="G6" t="s">
+        <v>19</v>
+      </c>
+      <c r="H6" t="s">
+        <v>20</v>
+      </c>
+      <c r="I6" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="J6" t="s">
+        <v>43</v>
+      </c>
+      <c r="K6" t="s">
+        <v>43</v>
+      </c>
+      <c r="L6" t="s">
+        <v>19</v>
+      </c>
+      <c r="M6" t="s">
+        <v>43</v>
+      </c>
+      <c r="N6" t="s">
+        <v>43</v>
+      </c>
+      <c r="O6" t="s">
+        <v>21</v>
+      </c>
+      <c r="P6" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>21</v>
+      </c>
+      <c r="R6" t="s">
+        <v>64</v>
+      </c>
+      <c r="S6" t="s">
+        <v>21</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{31F51D46-88B1-476D-8CD7-42FBC0AD7317}">
+  <dimension ref="A1:S6"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="13.6640625" customWidth="1"/>
+    <col min="3" max="3" width="11.88671875" customWidth="1"/>
+    <col min="4" max="4" width="20" customWidth="1"/>
+    <col min="8" max="8" width="16" customWidth="1"/>
+    <col min="9" max="9" width="26.44140625" customWidth="1"/>
+    <col min="10" max="10" width="16" customWidth="1"/>
+    <col min="11" max="11" width="12.33203125" customWidth="1"/>
+    <col min="12" max="12" width="12.77734375" customWidth="1"/>
+    <col min="13" max="13" width="15.21875" customWidth="1"/>
+    <col min="14" max="15" width="14.77734375" customWidth="1"/>
+    <col min="17" max="17" width="19.21875" customWidth="1"/>
+    <col min="18" max="18" width="23" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:19" ht="101.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="O1" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="P1" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q1" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="R1" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="2" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F2" s="3">
+        <v>46060</v>
+      </c>
+      <c r="G2" t="s">
+        <v>19</v>
+      </c>
+      <c r="H2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K2" t="s">
+        <v>43</v>
+      </c>
+      <c r="L2" t="s">
+        <v>19</v>
+      </c>
+      <c r="M2" t="s">
+        <v>43</v>
+      </c>
+      <c r="N2" t="s">
+        <v>23</v>
+      </c>
+      <c r="O2" t="s">
+        <v>21</v>
+      </c>
+      <c r="P2" t="s">
+        <v>74</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>21</v>
+      </c>
+      <c r="R2" t="s">
+        <v>64</v>
+      </c>
+      <c r="S2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D3" t="s">
+        <v>30</v>
+      </c>
+      <c r="E3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F3" s="3">
+        <v>46060</v>
+      </c>
+      <c r="G3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H3" t="s">
+        <v>20</v>
+      </c>
+      <c r="I3" t="s">
+        <v>31</v>
+      </c>
+      <c r="J3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K3" t="s">
+        <v>43</v>
+      </c>
+      <c r="L3" t="s">
+        <v>19</v>
+      </c>
+      <c r="M3" t="s">
+        <v>43</v>
+      </c>
+      <c r="N3" t="s">
+        <v>23</v>
+      </c>
+      <c r="O3" t="s">
+        <v>21</v>
+      </c>
+      <c r="P3" t="s">
+        <v>78</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>21</v>
+      </c>
+      <c r="R3" t="s">
+        <v>64</v>
+      </c>
+      <c r="S3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>35</v>
+      </c>
+      <c r="C4" t="s">
+        <v>36</v>
+      </c>
+      <c r="D4" t="s">
+        <v>32</v>
+      </c>
+      <c r="E4" t="s">
+        <v>18</v>
+      </c>
+      <c r="F4" s="3">
+        <v>46060</v>
+      </c>
+      <c r="G4" t="s">
+        <v>19</v>
+      </c>
+      <c r="H4" t="s">
+        <v>20</v>
+      </c>
+      <c r="I4" t="s">
+        <v>33</v>
+      </c>
+      <c r="J4" t="s">
+        <v>20</v>
+      </c>
+      <c r="K4" t="s">
+        <v>43</v>
+      </c>
+      <c r="L4" t="s">
+        <v>19</v>
+      </c>
+      <c r="M4" t="s">
+        <v>43</v>
+      </c>
+      <c r="N4" t="s">
+        <v>23</v>
+      </c>
+      <c r="O4" t="s">
+        <v>21</v>
+      </c>
+      <c r="P4" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>21</v>
+      </c>
+      <c r="R4" t="s">
+        <v>64</v>
+      </c>
+      <c r="S4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>34</v>
+      </c>
+      <c r="C5" t="s">
+        <v>37</v>
+      </c>
+      <c r="D5" t="s">
+        <v>38</v>
+      </c>
+      <c r="E5" t="s">
+        <v>18</v>
+      </c>
+      <c r="F5" s="3">
+        <v>46060</v>
+      </c>
+      <c r="G5" t="s">
+        <v>19</v>
+      </c>
+      <c r="H5" t="s">
+        <v>20</v>
+      </c>
+      <c r="I5" t="s">
+        <v>39</v>
+      </c>
+      <c r="J5" t="s">
+        <v>20</v>
+      </c>
+      <c r="K5" t="s">
+        <v>43</v>
+      </c>
+      <c r="L5" t="s">
+        <v>19</v>
+      </c>
+      <c r="M5" t="s">
+        <v>43</v>
+      </c>
+      <c r="N5" t="s">
+        <v>23</v>
+      </c>
+      <c r="O5" t="s">
+        <v>21</v>
+      </c>
+      <c r="P5" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>21</v>
+      </c>
+      <c r="R5" t="s">
+        <v>64</v>
+      </c>
+      <c r="S5" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>40</v>
+      </c>
+      <c r="C6" t="s">
+        <v>40</v>
+      </c>
+      <c r="D6" t="s">
+        <v>41</v>
+      </c>
+      <c r="E6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F6" s="3">
+        <v>46060</v>
+      </c>
+      <c r="G6" t="s">
+        <v>19</v>
+      </c>
+      <c r="H6" t="s">
+        <v>20</v>
+      </c>
+      <c r="I6" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="J6" t="s">
+        <v>20</v>
+      </c>
+      <c r="K6" t="s">
+        <v>43</v>
+      </c>
+      <c r="L6" t="s">
+        <v>19</v>
+      </c>
+      <c r="M6" t="s">
+        <v>43</v>
+      </c>
+      <c r="N6" t="s">
+        <v>23</v>
+      </c>
+      <c r="O6" t="s">
+        <v>21</v>
+      </c>
+      <c r="P6" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>21</v>
+      </c>
+      <c r="R6" t="s">
+        <v>64</v>
+      </c>
+      <c r="S6" t="s">
+        <v>21</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5C081DE9-EF7F-4394-B2AD-7F39C156AD0A}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
